--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT-A.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT-A.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>KIT-A VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
+          <t>KIT-A CABEÇOTE  VEDAMOTOS TWISTER CBX250/ TORNADO XR250</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -457,7 +457,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -470,7 +474,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>KIT-A VEDAMOTOS FAN TITAN CG125 2009/ CBF125</t>
+          <t>KIT-A CABEÇOTE  VEDAMOTOS FAN TITAN CG125 2009/ CBF125</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -478,7 +482,11 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -491,7 +499,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KIT-A VEDAMOTOS TITAN FAN150 2004/ BROS NXR150 2006 FLEX</t>
+          <t>KIT-A CABEÇOTE  VEDAMOTOS TITAN FAN150 2004/ BROS NXR150 2006 FLEX</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -499,7 +507,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -512,7 +524,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>KIT-A VEDAMOTOS TITAN FAN150 2004/ BROS NXR150 2006 FLEX</t>
+          <t>KIT-A CABEÇOTE  VEDAMOTOS TITAN FAN150 2004/ BROS NXR150 2006 FLEX</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -520,7 +532,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -533,7 +549,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KIT-A VEDAMOTOS TITAN CG 2000 KS ES</t>
+          <t>KIT-A CABEÇOTE  VEDAMOTOS TITAN CG 2000 KS ES</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -541,7 +557,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -554,7 +574,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>KIT-A EMBUS POP110I 2016 A 2023/ BIZ110I 2016 A 2023</t>
+          <t>KIT-A CABEÇOTE  EMBUS POP110I 2016 A 2023/ BIZ110I 2016 A 2023</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -562,7 +582,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -575,7 +599,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KIT-A EMBUS FACTOR FAZER XTZ150 2014 A 2020</t>
+          <t>KIT-A CABEÇOTE  EMBUS FACTOR FAZER XTZ150 2014 A 2020</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -600,7 +624,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KIT-A VEDAMOTOS FAZER YS250</t>
+          <t>KIT-A CABEÇOTE  VEDAMOTOS FAZER YS250</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -608,7 +632,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -621,7 +649,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>KIT-A VEDAMOTOS CB250F TWISTER 2016</t>
+          <t>KIT-A CABEÇOTE  VEDAMOTOS CB250F TWISTER 2016</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -646,7 +674,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>KIT-A BRAVIC TITAN FAN160 2016 A 2021 BMA48112</t>
+          <t>KIT-A CABEÇOTE  BRAVIC TITAN FAN160 2016 A 2021 BMA48112</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -671,7 +699,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KIT-A VALFLEX CB300 2009 A 2015</t>
+          <t>KIT-A CABEÇOTE  VALFLEX CB300 2009 A 2015</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -679,7 +707,11 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -692,7 +724,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>KIT-A VALFLEX TITAN 2000 KS ES</t>
+          <t>KIT-A CABEÇOTE  VALFLEX TITAN 2000 KS ES</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -700,7 +732,11 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -713,7 +749,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KIT-A IRON SUSUKI YES125 176266</t>
+          <t>KIT-A CABEÇOTE  IRON SUSUKI YES125 176266</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -738,7 +774,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KIT-A VEDAMOTOS YS FAZER XTZ CROSSER 150 2016</t>
+          <t>KIT-A CABEÇOTE  VEDAMOTOS YS FAZER XTZ CROSSER 150 2016</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -746,7 +782,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -759,7 +799,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT-A VEDAMOTOS BROS NXR CG TITAN FAN160 </t>
+          <t xml:space="preserve">KIT-A CABEÇOTE  VEDAMOTOS BROS NXR CG TITAN FAN160 </t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -767,7 +807,11 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -780,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">KIT-A EMBUS POP110I/ BIZ110I </t>
+          <t xml:space="preserve">KIT-A CABEÇOTE  EMBUS POP110I/ BIZ110I </t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -788,7 +832,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -801,7 +849,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN CB300/ XRE300</t>
+          <t>KIT-A CABEÇOTE  WW3 CB300/ XRE300</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -809,7 +857,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -822,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN TWISTER CBX250/ XR 250 TORNADO</t>
+          <t>KIT-A CABEÇOTE  JAPAN TWISTER CBX250/ XR 250 TORNADO</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -830,7 +882,11 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -843,7 +899,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN TITAN FAN CG150 1104015</t>
+          <t>KIT-A CABEÇOTE  JAPAN TITAN FAN CG150 1104015</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -851,7 +907,11 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -864,7 +924,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN CG125 1992 A 1998/ TITAN 2000 KS 1104225</t>
+          <t>KIT-A CABEÇOTE  JAPAN CG125 1992 A 1998/ TITAN 2000 KS 1104225</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -872,7 +932,11 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -885,7 +949,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN FAN CG125 2000 A 2006 1104015</t>
+          <t>KIT-A CABEÇOTE  JAPAN FAN CG125 2000 A 2006 1104015</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -893,7 +957,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -906,7 +974,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN BIZ125 1104010</t>
+          <t>KIT-A CABEÇOTE  JAPAN BIZ125 1104010</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -914,7 +982,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -927,7 +999,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN SUSUKI YES125 1250308</t>
+          <t>KIT-A CABEÇOTE  JAPAN SUSUKI YES125 1250308</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -935,7 +1007,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -948,7 +1024,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN FAZER150 1211850</t>
+          <t>KIT-A CABEÇOTE  JAPAN FAZER150 1211850</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -956,7 +1032,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -969,7 +1049,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KIT-A JAPAN BIZ110 2015 1105248</t>
+          <t>KIT-A CABEÇOTE  JAPAN BIZ110 2015 1105248</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -977,7 +1057,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -990,7 +1074,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>KIT-A PEÇA+ CG 1992/ TITAN 2000 KS/ BROX NXR125</t>
+          <t>KIT-A CABEÇOTE  PEÇA+ CG 1992/ TITAN 2000 KS/ BROX NXR125</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -998,7 +1082,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT-A.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/KIT-A.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:D27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,11 +452,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -482,11 +472,6 @@
           <t>9</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -507,11 +492,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -532,11 +512,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -557,11 +532,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -582,11 +552,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,11 +572,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -632,11 +592,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,11 +612,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -682,11 +632,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -707,11 +652,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -732,11 +672,6 @@
           <t>6</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -757,11 +692,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -782,11 +712,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -807,11 +732,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -832,11 +752,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -857,11 +772,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -882,11 +792,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -907,11 +812,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -932,11 +832,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -957,11 +852,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -982,11 +872,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1007,11 +892,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1032,11 +912,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1057,11 +932,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1080,11 +950,6 @@
       <c r="D27" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
